--- a/data_xlsx_archive/志明AI實驗數據_6_1-6_12.xlsx
+++ b/data_xlsx_archive/志明AI實驗數據_6_1-6_12.xlsx
@@ -124,10 +124,10 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Jpan" typeface="ï¼­ï¼³ ï¼°ã´ã·ãã¯"/>
+        <a:font script="Hang" typeface="ë§ì ê³ ë"/>
+        <a:font script="Hans" typeface="å®ä½"/>
+        <a:font script="Hant" typeface="æ°ç´°æé«"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -159,10 +159,10 @@
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Jpan" typeface="ï¼­ï¼³ ï¼°ã´ã·ãã¯"/>
+        <a:font script="Hang" typeface="ë§ì ê³ ë"/>
+        <a:font script="Hans" typeface="å®ä½"/>
+        <a:font script="Hant" typeface="æ°ç´°æé«"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -400,19 +400,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:N20"/>
   <cols>
-    <col min="1" max="1" width="4.83203125" customWidth="1"/>
-    <col min="2" max="2" width="6.83203125" customWidth="1"/>
-    <col min="3" max="3" width="26.83203125" customWidth="1"/>
-    <col min="4" max="4" width="10.83203125" customWidth="1"/>
-    <col min="5" max="5" width="10.83203125" customWidth="1"/>
-    <col min="6" max="6" width="10.83203125" customWidth="1"/>
-    <col min="7" max="7" width="10.83203125" customWidth="1"/>
-    <col min="8" max="8" width="10.83203125" customWidth="1"/>
-    <col min="9" max="9" width="10.83203125" customWidth="1"/>
-    <col min="10" max="10" width="8.83203125" customWidth="1"/>
-    <col min="11" max="11" width="22.83203125" customWidth="1"/>
+    <col min="1" max="1" customWidth="1" width="4.83203125"/>
+    <col min="2" max="2" customWidth="1" width="6.83203125"/>
+    <col min="3" max="3" customWidth="1" width="26.83203125"/>
+    <col min="4" max="4" customWidth="1" width="10.83203125"/>
+    <col min="5" max="5" customWidth="1" width="10.83203125"/>
+    <col min="6" max="6" customWidth="1" width="10.83203125"/>
+    <col min="7" max="7" customWidth="1" width="10.83203125"/>
+    <col min="8" max="8" customWidth="1" width="10.83203125"/>
+    <col min="9" max="9" customWidth="1" width="10.83203125"/>
+    <col min="10" max="10" customWidth="1" width="8.83203125"/>
+    <col min="11" max="11" customWidth="1" width="22.83203125"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -447,6 +447,15 @@
         <v>分類</v>
       </c>
       <c r="K1" t="str">
+        <v>圖像ER%</v>
+      </c>
+      <c r="L1" t="str">
+        <v>連結ER%</v>
+      </c>
+      <c r="M1" t="str">
+        <v>ER差距(pp)</v>
+      </c>
+      <c r="N1" t="str">
         <v>備註</v>
       </c>
     </row>
@@ -481,7 +490,16 @@
       <c r="J2" t="str">
         <v>財經</v>
       </c>
-      <c r="K2" t="str">
+      <c r="K2">
+        <v>0.551</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0.551</v>
+      </c>
+      <c r="N2" t="str">
         <v>圖像欄為瀏覽人數</v>
       </c>
     </row>
@@ -516,7 +534,16 @@
       <c r="J3" t="str">
         <v>財經</v>
       </c>
-      <c r="K3" t="str">
+      <c r="K3">
+        <v>1.887</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>1.887</v>
+      </c>
+      <c r="N3" t="str">
         <v/>
       </c>
     </row>
@@ -551,7 +578,16 @@
       <c r="J4" t="str">
         <v>環境</v>
       </c>
-      <c r="K4" t="str">
+      <c r="K4">
+        <v>1.515</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>1.515</v>
+      </c>
+      <c r="N4" t="str">
         <v/>
       </c>
     </row>
@@ -586,7 +622,16 @@
       <c r="J5" t="str">
         <v>環境</v>
       </c>
-      <c r="K5" t="str">
+      <c r="K5">
+        <v>0.64</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0.64</v>
+      </c>
+      <c r="N5" t="str">
         <v/>
       </c>
     </row>
@@ -621,7 +666,16 @@
       <c r="J6" t="str">
         <v>政治</v>
       </c>
-      <c r="K6" t="str">
+      <c r="K6">
+        <v>0.948</v>
+      </c>
+      <c r="L6">
+        <v>0.377</v>
+      </c>
+      <c r="M6">
+        <v>0.571</v>
+      </c>
+      <c r="N6" t="str">
         <v/>
       </c>
     </row>
@@ -656,7 +710,16 @@
       <c r="J7" t="str">
         <v>政治</v>
       </c>
-      <c r="K7" t="str">
+      <c r="K7">
+        <v>27.273</v>
+      </c>
+      <c r="L7">
+        <v>20</v>
+      </c>
+      <c r="M7">
+        <v>7.273</v>
+      </c>
+      <c r="N7" t="str">
         <v/>
       </c>
     </row>
@@ -691,7 +754,16 @@
       <c r="J8" t="str">
         <v>政治</v>
       </c>
-      <c r="K8" t="str">
+      <c r="K8">
+        <v>0.851</v>
+      </c>
+      <c r="L8">
+        <v>0.909</v>
+      </c>
+      <c r="M8">
+        <v>-0.058</v>
+      </c>
+      <c r="N8" t="str">
         <v/>
       </c>
     </row>
@@ -726,7 +798,16 @@
       <c r="J9" t="str">
         <v>政治</v>
       </c>
-      <c r="K9" t="str">
+      <c r="K9">
+        <v>2.137</v>
+      </c>
+      <c r="L9">
+        <v>0.943</v>
+      </c>
+      <c r="M9">
+        <v>1.194</v>
+      </c>
+      <c r="N9" t="str">
         <v/>
       </c>
     </row>
@@ -761,7 +842,16 @@
       <c r="J10" t="str">
         <v>社會</v>
       </c>
-      <c r="K10" t="str">
+      <c r="K10">
+        <v>2.343</v>
+      </c>
+      <c r="L10">
+        <v>2.381</v>
+      </c>
+      <c r="M10">
+        <v>-0.038</v>
+      </c>
+      <c r="N10" t="str">
         <v/>
       </c>
     </row>
@@ -796,7 +886,16 @@
       <c r="J11" t="str">
         <v>社會</v>
       </c>
-      <c r="K11" t="str">
+      <c r="K11">
+        <v>0.314</v>
+      </c>
+      <c r="L11">
+        <v>0.732</v>
+      </c>
+      <c r="M11">
+        <v>-0.418</v>
+      </c>
+      <c r="N11" t="str">
         <v>互動差距 1，同豬肉情況</v>
       </c>
     </row>
@@ -831,7 +930,16 @@
       <c r="J12" t="str">
         <v>社會</v>
       </c>
-      <c r="K12" t="str">
+      <c r="K12">
+        <v>1.406</v>
+      </c>
+      <c r="L12">
+        <v>1.235</v>
+      </c>
+      <c r="M12">
+        <v>0.171</v>
+      </c>
+      <c r="N12" t="str">
         <v/>
       </c>
     </row>
@@ -866,7 +974,16 @@
       <c r="J13" t="str">
         <v>社會</v>
       </c>
-      <c r="K13" t="str">
+      <c r="K13">
+        <v>1.083</v>
+      </c>
+      <c r="L13">
+        <v>1.205</v>
+      </c>
+      <c r="M13">
+        <v>-0.122</v>
+      </c>
+      <c r="N13" t="str">
         <v/>
       </c>
     </row>
@@ -901,7 +1018,16 @@
       <c r="J14" t="str">
         <v>政治</v>
       </c>
-      <c r="K14" t="str">
+      <c r="K14">
+        <v>0.987</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>0.987</v>
+      </c>
+      <c r="N14" t="str">
         <v/>
       </c>
     </row>
@@ -936,7 +1062,16 @@
       <c r="J15" t="str">
         <v>環境</v>
       </c>
-      <c r="K15" t="str">
+      <c r="K15">
+        <v>0.826</v>
+      </c>
+      <c r="L15">
+        <v>0.87</v>
+      </c>
+      <c r="M15">
+        <v>-0.044</v>
+      </c>
+      <c r="N15" t="str">
         <v/>
       </c>
     </row>
@@ -971,7 +1106,16 @@
       <c r="J16" t="str">
         <v>財經</v>
       </c>
-      <c r="K16" t="str">
+      <c r="K16">
+        <v>0.475</v>
+      </c>
+      <c r="L16">
+        <v>1.158</v>
+      </c>
+      <c r="M16">
+        <v>-0.683</v>
+      </c>
+      <c r="N16" t="str">
         <v>互動差距 1，視為持平</v>
       </c>
     </row>
@@ -1006,7 +1150,16 @@
       <c r="J17" t="str">
         <v>社會</v>
       </c>
-      <c r="K17" t="str">
+      <c r="K17">
+        <v>1.195</v>
+      </c>
+      <c r="L17">
+        <v>1.604</v>
+      </c>
+      <c r="M17">
+        <v>-0.409</v>
+      </c>
+      <c r="N17" t="str">
         <v/>
       </c>
     </row>
@@ -1041,7 +1194,16 @@
       <c r="J18" t="str">
         <v>社會</v>
       </c>
-      <c r="K18" t="str">
+      <c r="K18">
+        <v>16.667</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>16.667</v>
+      </c>
+      <c r="N18" t="str">
         <v/>
       </c>
     </row>
@@ -1076,7 +1238,16 @@
       <c r="J19" t="str">
         <v>政治</v>
       </c>
-      <c r="K19" t="str">
+      <c r="K19">
+        <v>1.232</v>
+      </c>
+      <c r="L19">
+        <v>1.176</v>
+      </c>
+      <c r="M19">
+        <v>0.056</v>
+      </c>
+      <c r="N19" t="str">
         <v/>
       </c>
     </row>
@@ -1111,13 +1282,22 @@
       <c r="J20" t="str">
         <v>社會</v>
       </c>
-      <c r="K20" t="str">
+      <c r="K20">
+        <v>0.714</v>
+      </c>
+      <c r="L20">
+        <v>1.389</v>
+      </c>
+      <c r="M20">
+        <v>-0.675</v>
+      </c>
+      <c r="N20" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K20"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N20"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1126,16 +1306,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J6"/>
   <cols>
-    <col min="1" max="1" width="4.83203125" customWidth="1"/>
-    <col min="2" max="2" width="6.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-    <col min="4" max="4" width="12.83203125" customWidth="1"/>
-    <col min="5" max="5" width="12.83203125" customWidth="1"/>
-    <col min="6" max="6" width="10.83203125" customWidth="1"/>
-    <col min="7" max="7" width="10.83203125" customWidth="1"/>
-    <col min="8" max="8" width="12.83203125" customWidth="1"/>
-    <col min="9" max="9" width="6.83203125" customWidth="1"/>
-    <col min="10" max="10" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" customWidth="1" width="4.83203125"/>
+    <col min="2" max="2" customWidth="1" width="6.83203125"/>
+    <col min="3" max="3" customWidth="1" width="22.83203125"/>
+    <col min="4" max="4" customWidth="1" width="12.83203125"/>
+    <col min="5" max="5" customWidth="1" width="12.83203125"/>
+    <col min="6" max="6" customWidth="1" width="10.83203125"/>
+    <col min="7" max="7" customWidth="1" width="10.83203125"/>
+    <col min="8" max="8" customWidth="1" width="12.83203125"/>
+    <col min="9" max="9" customWidth="1" width="6.83203125"/>
+    <col min="10" max="10" customWidth="1" width="8.83203125"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1341,16 +1521,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J2"/>
   <cols>
-    <col min="1" max="1" width="4.83203125" customWidth="1"/>
-    <col min="2" max="2" width="6.83203125" customWidth="1"/>
-    <col min="3" max="3" width="20.83203125" customWidth="1"/>
-    <col min="4" max="4" width="14.83203125" customWidth="1"/>
-    <col min="5" max="5" width="14.83203125" customWidth="1"/>
-    <col min="6" max="6" width="10.83203125" customWidth="1"/>
-    <col min="7" max="7" width="14.83203125" customWidth="1"/>
-    <col min="8" max="8" width="14.83203125" customWidth="1"/>
-    <col min="9" max="9" width="20.83203125" customWidth="1"/>
-    <col min="10" max="10" width="22.83203125" customWidth="1"/>
+    <col min="1" max="1" customWidth="1" width="4.83203125"/>
+    <col min="2" max="2" customWidth="1" width="6.83203125"/>
+    <col min="3" max="3" customWidth="1" width="20.83203125"/>
+    <col min="4" max="4" customWidth="1" width="14.83203125"/>
+    <col min="5" max="5" customWidth="1" width="14.83203125"/>
+    <col min="6" max="6" customWidth="1" width="10.83203125"/>
+    <col min="7" max="7" customWidth="1" width="14.83203125"/>
+    <col min="8" max="8" customWidth="1" width="14.83203125"/>
+    <col min="9" max="9" customWidth="1" width="20.83203125"/>
+    <col min="10" max="10" customWidth="1" width="22.83203125"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1428,8 +1608,8 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B12"/>
   <cols>
-    <col min="1" max="1" width="22.83203125" customWidth="1"/>
-    <col min="2" max="2" width="50.83203125" customWidth="1"/>
+    <col min="1" max="1" customWidth="1" width="22.83203125"/>
+    <col min="2" max="2" customWidth="1" width="50.83203125"/>
   </cols>
   <sheetData>
     <row r="1">
